--- a/Excel/pub_stock.xlsx
+++ b/Excel/pub_stock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,46 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>market</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>209</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GVREIT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Property &amp; Construction</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SET</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>655</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TFFIF</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SET</t>
         </is>
       </c>
     </row>

--- a/Excel/pub_stock.xlsx
+++ b/Excel/pub_stock.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,46 +450,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>209</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>GVREIT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Property &amp; Construction</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>655</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TFFIF</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SET</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
